--- a/data/trans_camb/P5B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,66</t>
+          <t>-4,74; -0,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,33</t>
+          <t>-3,42; 2,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,65</t>
+          <t>-4,91; -0,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; -0,56</t>
+          <t>-4,87; -0,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 1,12</t>
+          <t>-4,09; 1,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; -0,08</t>
+          <t>-4,99; -0,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,88</t>
+          <t>-3,96; -0,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,68</t>
+          <t>-2,89; 0,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,69</t>
+          <t>-3,76; -0,72</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-65,46%</t>
+          <t>-65,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-49,16%</t>
+          <t>-48,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 101,42</t>
+          <t>-100,0; 117,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -18,31</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 2,13</t>
+          <t>-5,93; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,57; -1,28</t>
+          <t>-7,82; -1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,67; -2,12</t>
+          <t>-8,34; -2,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 2,21</t>
+          <t>-5,11; 2,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -0,83</t>
+          <t>-6,97; -0,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; -1,88</t>
+          <t>-7,89; -1,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,16</t>
+          <t>-3,96; 1,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; -1,67</t>
+          <t>-5,97; -1,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,06; -2,64</t>
+          <t>-6,73; -2,57</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-31,67%</t>
+          <t>-31,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-83,77%</t>
+          <t>-83,72%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -971,17 +971,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-92,01%</t>
+          <t>-91,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-31,7%</t>
+          <t>-31,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-78,96%</t>
+          <t>-78,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,36; 98,01</t>
+          <t>-82,05; 90,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -18,37</t>
+          <t>-100,0; 4,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-78,49; 91,44</t>
+          <t>-77,14; 100,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-99,68; -5,59</t>
+          <t>-94,27; -11,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,58</t>
+          <t>-100,0; -31,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 40,22</t>
+          <t>-67,07; 42,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-93,07; -40,98</t>
+          <t>-93,62; -42,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -71,21</t>
+          <t>-100,0; -71,46</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,23</t>
+          <t>-3,64; 0,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,51</t>
+          <t>-1,65; 4,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 46,27</t>
+          <t>-1,98; 48,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,69</t>
+          <t>-2,04; 2,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,25</t>
+          <t>-1,94; 2,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,0</t>
+          <t>-3,64; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,13</t>
+          <t>-2,25; 1,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,58</t>
+          <t>-1,1; 2,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 27,38</t>
+          <t>-1,57; 30,93</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 730,22</t>
+          <t>-60,3; 694,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,23; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-91,67; 204,91</t>
+          <t>-90,01; 173,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,94; 374,29</t>
+          <t>-55,12; 408,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-89,7; 5532,97</t>
+          <t>-88,49; —</t>
         </is>
       </c>
     </row>
@@ -1272,39 +1272,39 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,78</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,71</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>-2,35</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>-2,37</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,97</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
           <t>-2,43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-3,79</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,72</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,37</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-2,45</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>-3,1</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-1,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 1,64</t>
+          <t>-6,76; 1,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,72; -0,46</t>
+          <t>-7,86; -0,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,79; -0,69</t>
+          <t>-7,53; -0,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 0,16</t>
+          <t>-5,28; 0,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,28</t>
+          <t>-5,25; 0,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 5,03</t>
+          <t>-2,63; 4,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,15</t>
+          <t>-4,99; 0,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; -0,98</t>
+          <t>-5,64; -1,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,23</t>
+          <t>-3,82; 1,27</t>
         </is>
       </c>
     </row>
@@ -1378,22 +1378,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-43,79%</t>
+          <t>-43,51%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-68,46%</t>
+          <t>-68,32%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-67,18%</t>
+          <t>-67,03%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-64,81%</t>
+          <t>-64,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1403,22 +1403,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-52,98%</t>
+          <t>-52,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-67,13%</t>
+          <t>-67,05%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-29,48%</t>
+          <t>-29,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-78,81; 63,77</t>
+          <t>-84,1; 57,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,59; 4,01</t>
+          <t>-91,76; 0,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,11; -5,99</t>
+          <t>-92,1; -10,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,43</t>
+          <t>-100,0; 49,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,8; 49,2</t>
+          <t>-100,0; 39,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,36; 268,25</t>
+          <t>-51,52; 268,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-80,2; 3,31</t>
+          <t>-80,29; 11,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-87,74; -20,77</t>
+          <t>-88,48; -21,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,56; 40,68</t>
+          <t>-63,53; 38,07</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,12</t>
+          <t>-3,47; -0,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,43</t>
+          <t>-3,73; -0,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 14,71</t>
+          <t>-3,65; 12,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,01</t>
+          <t>-2,95; -0,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; -0,54</t>
+          <t>-3,24; -0,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; -0,42</t>
+          <t>-3,22; -0,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,65</t>
+          <t>-2,87; -0,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,95</t>
+          <t>-3,13; -0,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,83</t>
+          <t>-2,72; 5,66</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-47,24%</t>
+          <t>-47,1%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-53,49%</t>
+          <t>-53,28%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-48,55%</t>
+          <t>-48,41%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-63,38%</t>
+          <t>-63,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-57,55%</t>
+          <t>-57,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>-48,08%</t>
+          <t>-47,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-58,14%</t>
+          <t>-58,02%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,78%</t>
+          <t>-15,64%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -0,95</t>
+          <t>-72,84; -1,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,0; -14,11</t>
+          <t>-75,13; -14,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,54; 464,95</t>
+          <t>-87,6; 498,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,32; 4,31</t>
+          <t>-75,89; -0,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,44; -16,93</t>
+          <t>-82,83; -22,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,09; -16,51</t>
+          <t>-79,43; -11,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,89; -21,84</t>
+          <t>-70,72; -19,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-74,46; -31,68</t>
+          <t>-75,54; -33,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,79; 194,8</t>
+          <t>-76,23; 183,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; -0,64</t>
+          <t>-5,29; -0,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,43</t>
+          <t>-3,92; 2,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; -0,64</t>
+          <t>-5,86; -0,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; -0,56</t>
+          <t>-5,19; -0,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 1,09</t>
+          <t>-3,77; 1,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -0,16</t>
+          <t>-4,22; -0,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; -0,88</t>
+          <t>-4,17; -0,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,96</t>
+          <t>-3,05; 0,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -0,72</t>
+          <t>-3,85; -0,65</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 117,78</t>
+          <t>-100,0; 152,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -18,31</t>
+          <t>-100,0; -26,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 2,1</t>
+          <t>-5,11; 2,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; -1,35</t>
+          <t>-7,75; -1,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -2,1</t>
+          <t>-8,74; -2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,09</t>
+          <t>-4,88; 2,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,97; -0,9</t>
+          <t>-6,86; -0,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -1,9</t>
+          <t>-7,92; -1,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,23</t>
+          <t>-4,4; 1,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; -1,61</t>
+          <t>-6,21; -1,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; -2,57</t>
+          <t>-6,66; -2,42</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,05; 90,03</t>
+          <t>-77,94; 98,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,85</t>
+          <t>-100,0; -4,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,14; 100,7</t>
+          <t>-77,26; 92,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-94,27; -11,51</t>
+          <t>-94,51; 15,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -31,51</t>
+          <t>-100,0; -37,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-67,07; 42,0</t>
+          <t>-69,23; 41,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-93,62; -42,86</t>
+          <t>-94,23; -45,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -71,46</t>
+          <t>-100,0; -66,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,88</t>
+          <t>-3,89; 0,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,68</t>
+          <t>-1,78; 4,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 48,35</t>
+          <t>-2,05; 49,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,81</t>
+          <t>-1,96; 2,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,43</t>
+          <t>-1,74; 2,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,0</t>
+          <t>-4,53; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,13</t>
+          <t>-2,11; 1,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,73</t>
+          <t>-1,19; 2,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 30,93</t>
+          <t>-1,48; 32,03</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,3; 694,25</t>
+          <t>-70,37; 527,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>-88,21; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-90,01; 173,47</t>
+          <t>-85,82; 194,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,12; 408,81</t>
+          <t>-54,93; 345,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-88,49; —</t>
+          <t>-89,5; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 1,17</t>
+          <t>-6,26; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,86; -0,91</t>
+          <t>-7,41; -0,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -0,89</t>
+          <t>-7,79; -0,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,29</t>
+          <t>-5,2; 0,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,17</t>
+          <t>-5,57; 0,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,66</t>
+          <t>-2,74; 4,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,09</t>
+          <t>-4,92; -0,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -1,1</t>
+          <t>-5,47; -0,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 1,27</t>
+          <t>-4,25; 0,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 57,21</t>
+          <t>-82,58; 70,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,76; 0,82</t>
+          <t>-93,09; -1,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-92,1; -10,33</t>
+          <t>-91,93; -2,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,11</t>
+          <t>-100,0; 58,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,88</t>
+          <t>-100,0; 39,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,52; 268,03</t>
+          <t>-57,98; 241,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-80,29; 11,96</t>
+          <t>-82,58; -3,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,48; -21,88</t>
+          <t>-88,24; -22,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 38,07</t>
+          <t>-65,19; 27,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,09</t>
+          <t>-3,46; -0,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,54</t>
+          <t>-3,57; -0,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 12,78</t>
+          <t>-3,54; 14,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,1</t>
+          <t>-2,91; -0,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,59</t>
+          <t>-3,21; -0,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,36</t>
+          <t>-3,05; -0,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,87; -0,58</t>
+          <t>-2,78; -0,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -0,97</t>
+          <t>-3,04; -0,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 5,66</t>
+          <t>-2,78; 7,16</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,84; -1,56</t>
+          <t>-74,47; -4,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,13; -14,4</t>
+          <t>-73,98; -10,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-87,6; 498,65</t>
+          <t>-86,94; 425,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,89; -0,24</t>
+          <t>-75,69; 2,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-82,83; -22,11</t>
+          <t>-83,15; -20,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-79,43; -11,62</t>
+          <t>-77,36; -13,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -19,61</t>
+          <t>-68,26; -14,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-75,54; -33,51</t>
+          <t>-73,63; -29,8</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,23; 183,81</t>
+          <t>-75,77; 263,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P5B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P5B_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-2,11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-2,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-2,06</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-1,86</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; -0,65</t>
+          <t>-5,44; -0,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,79</t>
+          <t>-4,21; 0,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; -0,65</t>
+          <t>-4,81; -0,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; -0,56</t>
+          <t>-5,38; -0,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,01</t>
+          <t>-3,35; 2,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,13</t>
+          <t>-5,38; -0,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,88</t>
+          <t>-4,03; -0,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,87</t>
+          <t>-3,12; 0,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,65</t>
+          <t>-3,72; -0,68</t>
         </is>
       </c>
     </row>
@@ -735,34 +735,34 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>-65,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-81,8%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>-29,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-65,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-83,63%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>-48,99%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-90,85%</t>
+          <t>-90,48%</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 152,24</t>
+          <t>-100,0; 126,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -26,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -845,34 +845,34 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>-3,45</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,21</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>-3,89</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-4,65</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-1,46</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,45</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-4,24</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>-3,65</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,42</t>
+          <t>-4,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 2,54</t>
+          <t>-5,23; 2,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -1,15</t>
+          <t>-6,94; -0,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,74; -2,09</t>
+          <t>-8,0; -1,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,11</t>
+          <t>-5,86; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,86; -0,75</t>
+          <t>-7,81; -1,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -1,97</t>
+          <t>-8,67; -2,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,16</t>
+          <t>-4,06; 1,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -1,71</t>
+          <t>-6,01; -1,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -2,42</t>
+          <t>-6,86; -2,5</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-31,72%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-74,76%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-91,34%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-31,4%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-83,72%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-31,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-74,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-91,99%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>-31,58%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-95,44%</t>
+          <t>-95,15%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,94; 98,34</t>
+          <t>-78,49; 91,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,63</t>
+          <t>-99,68; -5,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; -26,69</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-82,64; 95,79</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; -15,44</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-77,26; 92,8</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-94,51; 15,5</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -37,83</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-69,23; 41,81</t>
+          <t>-67,25; 41,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,23; -45,86</t>
+          <t>-93,01; -42,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -66,48</t>
+          <t>-100,0; -64,85</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,04</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,07</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,44</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,78</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,07</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>-0,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,96</t>
+          <t>-1,75; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,45</t>
+          <t>-2,13; 2,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 49,14</t>
+          <t>-3,71; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,79</t>
+          <t>-3,71; 1,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,6</t>
+          <t>-1,86; 4,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,0</t>
+          <t>-2,47; 7,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,29</t>
+          <t>-2,16; 1,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,57</t>
+          <t>-1,03; 2,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 32,03</t>
+          <t>-2,0; 2,59</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-53,56%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>70,25%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>624,22%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>385,06%</t>
+          <t>-18,06%</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 527,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-88,21; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,09; 635,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,82; 194,96</t>
+          <t>-91,67; 204,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,93; 345,0</t>
+          <t>-59,47; 347,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-89,5; —</t>
+          <t>-92,11; 579,41</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,37</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,78</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,71</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,37</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>-3,67</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 1,56</t>
+          <t>-5,3; 0,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -0,56</t>
+          <t>-5,24; 0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,79; -0,68</t>
+          <t>-2,3; 4,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,51</t>
+          <t>-6,46; 1,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,2</t>
+          <t>-7,73; -0,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,65</t>
+          <t>-7,48; -0,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -0,14</t>
+          <t>-4,86; -0,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,47; -0,9</t>
+          <t>-5,72; -1,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,87</t>
+          <t>-3,88; 1,26</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-64,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-65,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27,54%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-43,51%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-68,32%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-67,03%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-64,47%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-65,0%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>-66,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-29,14%</t>
+          <t>-29,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-82,58; 70,41</t>
+          <t>-100,0; 44,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-93,09; -1,28</t>
+          <t>-92,8; 49,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,93; -2,34</t>
+          <t>-47,16; 265,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,7</t>
+          <t>-83,22; 46,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 39,57</t>
+          <t>-91,92; 0,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,98; 241,36</t>
+          <t>-91,68; -2,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-82,58; -3,26</t>
+          <t>-83,2; 4,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-88,24; -22,16</t>
+          <t>-89,37; -24,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 27,86</t>
+          <t>-63,58; 41,83</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-2,04</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-2,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,18</t>
+          <t>-3,08; 0,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,4</t>
+          <t>-3,36; -0,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 14,19</t>
+          <t>-3,19; -0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,17</t>
+          <t>-3,67; -0,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,59</t>
+          <t>-3,75; -0,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,37</t>
+          <t>-4,25; -0,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,54</t>
+          <t>-2,77; -0,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,89</t>
+          <t>-3,07; -1,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 7,16</t>
+          <t>-3,27; -1,13</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-48,41%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-63,33%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-56,03%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-47,1%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-53,28%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-48,41%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-63,33%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-57,46%</t>
+          <t>-69,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,64%</t>
+          <t>-63,56%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,47; -4,28</t>
+          <t>-76,73; 2,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,98; -10,43</t>
+          <t>-83,75; -24,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,94; 425,01</t>
+          <t>-79,71; -9,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,69; 2,51</t>
+          <t>-73,27; 4,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,15; -20,15</t>
+          <t>-75,39; -9,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-77,36; -13,2</t>
+          <t>-87,72; -19,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,26; -14,79</t>
+          <t>-67,48; -17,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-73,63; -29,8</t>
+          <t>-75,65; -31,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 263,92</t>
+          <t>-79,2; -37,13</t>
         </is>
       </c>
     </row>
